--- a/I-O Files/new_products.xlsx
+++ b/I-O Files/new_products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/161581077d7d95ba/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{BA4B2EB0-0030-4A7D-8424-F921B8B67E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D4D8474-F6F1-4A3F-9EA5-FCD4D144F354}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="8_{BA4B2EB0-0030-4A7D-8424-F921B8B67E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8F8C3B1-83A5-4C73-904A-5BF6B88E8982}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Title</t>
   </si>
@@ -46,67 +46,40 @@
     <t>ImagePath</t>
   </si>
   <si>
-    <t>Mouse1</t>
-  </si>
-  <si>
-    <t>Pen1</t>
-  </si>
-  <si>
-    <t>Shirt1</t>
-  </si>
-  <si>
-    <t>T-shirt1</t>
-  </si>
-  <si>
-    <t>Trousers1</t>
-  </si>
-  <si>
-    <t>water bottle1</t>
-  </si>
-  <si>
-    <t>good</t>
-  </si>
-  <si>
-    <t>ganesh</t>
-  </si>
-  <si>
-    <t>office use</t>
-  </si>
-  <si>
-    <t>SKU013</t>
-  </si>
-  <si>
-    <t>SKU014</t>
-  </si>
-  <si>
-    <t>SKU015</t>
-  </si>
-  <si>
-    <t>SKU016</t>
-  </si>
-  <si>
-    <t>SKU017</t>
-  </si>
-  <si>
-    <t>SKU018</t>
-  </si>
-  <si>
-    <t>D:\myProjects\ElitesecomTasks\I-O Files\img\watter bottle.jpg</t>
-  </si>
-  <si>
-    <t>D:\myProjects\ElitesecomTasks\I-O Files\img\Trousers.jpg</t>
-  </si>
-  <si>
-    <t>D:\myProjects\ElitesecomTasks\I-O Files\img\t-shirt.jpg</t>
-  </si>
-  <si>
-    <t>D:\myProjects\ElitesecomTasks\I-O Files\img\shirt.jpg</t>
-  </si>
-  <si>
-    <t>D:\myProjects\ElitesecomTasks\I-O Files\img\pen.jpg</t>
-  </si>
-  <si>
-    <t>D:\myProjects\ElitesecomTasks\I-O Files\img\mouse.jpg</t>
+    <t>logitech keyboard</t>
+  </si>
+  <si>
+    <t>good for long term use</t>
+  </si>
+  <si>
+    <t>logitech</t>
+  </si>
+  <si>
+    <t>computer accessories</t>
+  </si>
+  <si>
+    <t>SKU020</t>
+  </si>
+  <si>
+    <t>D:\myProjects\ElitesecomTasks\I-O Files\img\keyboard.jpeg</t>
+  </si>
+  <si>
+    <t>samsung power bank</t>
+  </si>
+  <si>
+    <t>good for use</t>
+  </si>
+  <si>
+    <t>samsung</t>
+  </si>
+  <si>
+    <t>mobile accessories</t>
+  </si>
+  <si>
+    <t>SKU021</t>
+  </si>
+  <si>
+    <t>D:\myProjects\ElitesecomTasks\I-O Files\img\POWER BANK.jpeg</t>
   </si>
 </sst>
 </file>
@@ -191,6 +164,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -480,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
@@ -520,155 +497,51 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>1500</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4">
-        <v>500</v>
-      </c>
-      <c r="F4" t="s">
         <v>19</v>
-      </c>
-      <c r="G4">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5">
-        <v>1000</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6">
-        <v>3000</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>50</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>10</v>
-      </c>
-      <c r="H7" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
